--- a/apps/backend/internal/profile/templates/ipra-high-risk-watchlist-template.xlsx
+++ b/apps/backend/internal/profile/templates/ipra-high-risk-watchlist-template.xlsx
@@ -82,12 +82,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18.00" customWidth="1"/>
-    <col min="2" max="2" width="14.00" customWidth="1"/>
-    <col min="3" max="3" width="34.00" customWidth="1"/>
+    <col min="2" max="2" width="34.00" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -97,11 +96,6 @@
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姓名</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">高风险原因</t>
         </is>
@@ -115,17 +109,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">张伟</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">跨境赌博关联，需重点核验出行目的</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1"/>
+  <autoFilter ref="A1:B1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/apps/backend/internal/profile/templates/ipra-high-risk-watchlist-template.xlsx
+++ b/apps/backend/internal/profile/templates/ipra-high-risk-watchlist-template.xlsx
@@ -82,39 +82,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18.00" customWidth="1"/>
     <col min="2" max="2" width="34.00" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高风险名单模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">证件号码</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">高风险原因</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">E92834102</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">跨境赌博关联，需重点核验出行目的</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <autoFilter ref="A2:B2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/apps/backend/internal/profile/templates/ipra-high-risk-watchlist-template.xlsx
+++ b/apps/backend/internal/profile/templates/ipra-high-risk-watchlist-template.xlsx
@@ -82,11 +82,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18.00" customWidth="1"/>
-    <col min="2" max="2" width="34.00" customWidth="1"/>
+    <col min="2" max="2" width="18.00" customWidth="1"/>
+    <col min="3" max="3" width="34.00" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -104,6 +105,11 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">风险类别</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">高风险原因</t>
         </is>
       </c>
@@ -116,15 +122,20 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">跨境赌博</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">跨境赌博关联，需重点核验出行目的</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <autoFilter ref="A2:B2"/>
+  <autoFilter ref="A2:C2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>